--- a/ploy/resources/sample/MiningBundleShop.xlsx
+++ b/ploy/resources/sample/MiningBundleShop.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\ploygame\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -54,12 +59,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-免费礼包
+2-看广告礼包
+3-付费礼包</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -70,6 +99,9 @@
     <t>序列</t>
   </si>
   <si>
+    <t>礼包类型</t>
+  </si>
+  <si>
     <t>礼包名称</t>
   </si>
   <si>
@@ -110,6 +142,9 @@
   </si>
   <si>
     <t>Order</t>
+  </si>
+  <si>
+    <t>BundleType</t>
   </si>
   <si>
     <t>BundleName</t>
@@ -374,12 +409,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1391,18 +1426,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="6" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="16.375" customWidth="1"/>
-    <col min="10" max="10" width="13.25" customWidth="1"/>
-    <col min="11" max="11" width="13.375" customWidth="1"/>
+    <col min="4" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="16.375" customWidth="1"/>
+    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="16.375" customWidth="1"/>
+    <col min="11" max="11" width="13.25" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1433,73 +1468,82 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1"/>
@@ -1511,8 +1555,9 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A13" si="0">B5*1000+C5</f>
         <v>6001</v>
@@ -1524,29 +1569,32 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
         <v>400800039</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1">
         <v>1024034</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>6002</v>
@@ -1558,29 +1606,32 @@
         <v>2</v>
       </c>
       <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
         <v>400800040</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>1024034</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6003</v>
@@ -1592,29 +1643,32 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
         <v>400800041</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1">
         <v>1024034</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="I7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="1">
         <v>5</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>6</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>6004</v>
@@ -1626,29 +1680,32 @@
         <v>4</v>
       </c>
       <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
         <v>400800042</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1024034</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1">
         <v>30</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1024034</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="1">
-        <v>5</v>
-      </c>
-      <c r="J8" s="1">
-        <v>30</v>
-      </c>
-      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>6005</v>
@@ -1660,29 +1717,32 @@
         <v>5</v>
       </c>
       <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
         <v>400800043</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="1">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1">
         <v>1024034</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="1">
         <v>5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>99</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6006</v>
@@ -1694,29 +1754,32 @@
         <v>6</v>
       </c>
       <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
         <v>400800044</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="1">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1">
         <v>1024035</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="1">
         <v>5</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>20</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>6007</v>
@@ -1728,29 +1791,32 @@
         <v>7</v>
       </c>
       <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
         <v>400800045</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="1">
+        <v>41</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="1">
         <v>1024035</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="I11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="1">
         <v>5</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>50</v>
       </c>
-      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>6008</v>
@@ -1762,29 +1828,32 @@
         <v>8</v>
       </c>
       <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
         <v>400800046</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="1">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="1">
         <v>1024036</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="I12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="1">
         <v>5</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>30</v>
       </c>
-      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>6009</v>
@@ -1796,27 +1865,30 @@
         <v>9</v>
       </c>
       <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2">
         <v>400800047</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="1">
+        <v>47</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="1">
         <v>1024036</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="I13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="1">
         <v>1</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>99</v>
       </c>
-      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ploy/resources/sample/MiningBundleShop.xlsx
+++ b/ploy/resources/sample/MiningBundleShop.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -186,6 +186,9 @@
     <t>镐*10</t>
   </si>
   <si>
+    <t>1980000_600</t>
+  </si>
+  <si>
     <t>基础礼包</t>
   </si>
   <si>
@@ -195,6 +198,9 @@
     <t>镐*50</t>
   </si>
   <si>
+    <t>1980000_3000</t>
+  </si>
+  <si>
     <t>进阶礼包</t>
   </si>
   <si>
@@ -204,6 +210,9 @@
     <t>镐*200</t>
   </si>
   <si>
+    <t>1980000_5000</t>
+  </si>
+  <si>
     <t>优享礼包</t>
   </si>
   <si>
@@ -213,6 +222,9 @@
     <t>炸弹*3</t>
   </si>
   <si>
+    <t>1980000_1200</t>
+  </si>
+  <si>
     <t>轻奢礼包</t>
   </si>
   <si>
@@ -231,6 +243,9 @@
     <t>挖掘*3</t>
   </si>
   <si>
+    <t>1980000_1500</t>
+  </si>
+  <si>
     <t>豪华礼包</t>
   </si>
   <si>
@@ -238,6 +253,9 @@
   </si>
   <si>
     <t>挖掘*10</t>
+  </si>
+  <si>
+    <t>1980000_5500</t>
   </si>
 </sst>
 </file>
@@ -1663,8 +1681,8 @@
       <c r="J7" s="1">
         <v>5</v>
       </c>
-      <c r="K7" s="1">
-        <v>6</v>
+      <c r="K7" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="L7" s="2"/>
     </row>
@@ -1686,22 +1704,22 @@
         <v>400800042</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="1">
         <v>1024034</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="K8" s="1">
-        <v>30</v>
+      <c r="K8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L8" s="2"/>
     </row>
@@ -1723,22 +1741,22 @@
         <v>400800043</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9" s="1">
         <v>1024034</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
-      <c r="K9" s="1">
-        <v>99</v>
+      <c r="K9" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="L9" s="2"/>
     </row>
@@ -1760,22 +1778,22 @@
         <v>400800044</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H10" s="1">
         <v>1024035</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
-      <c r="K10" s="1">
-        <v>20</v>
+      <c r="K10" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="L10" s="2"/>
     </row>
@@ -1797,22 +1815,22 @@
         <v>400800045</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H11" s="1">
         <v>1024035</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J11" s="1">
         <v>5</v>
       </c>
-      <c r="K11" s="1">
-        <v>50</v>
+      <c r="K11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L11" s="2"/>
     </row>
@@ -1834,22 +1852,22 @@
         <v>400800046</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H12" s="1">
         <v>1024036</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J12" s="1">
         <v>5</v>
       </c>
-      <c r="K12" s="1">
-        <v>30</v>
+      <c r="K12" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="L12" s="2"/>
     </row>
@@ -1871,22 +1889,22 @@
         <v>400800047</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H13" s="1">
         <v>1024036</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
-      <c r="K13" s="1">
-        <v>99</v>
+      <c r="K13" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="L13" s="2"/>
     </row>
